--- a/assets/constructions/examples/ctd_ma2.xlsx
+++ b/assets/constructions/examples/ctd_ma2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF6"/>
+  <dimension ref="A1:AK6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -589,11 +589,36 @@
           <t>apmx</t>
         </is>
       </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>GM4CH9006006-L15VTH</t>
+          <t>GM3CH90 06015-L15 VTH</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -619,7 +644,7 @@
         <v>5.9</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -650,7 +675,7 @@
         <v>58</v>
       </c>
       <c r="Q2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
@@ -697,13 +722,32 @@
         </is>
       </c>
       <c r="AF2" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>72.28</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AJ2" t="n">
+        <v>6352.15</v>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>PMKNS</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GM4CH9008012-L35VTH</t>
+          <t>GM4CH9006006-L15VTH</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -723,17 +767,17 @@
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>7.9</v>
+        <v>5.9</v>
       </c>
       <c r="G3" t="n">
-        <v>7.9</v>
+        <v>5.9</v>
       </c>
       <c r="H3" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>HA-8</t>
+          <t>HA-6</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -750,14 +794,14 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="P3" t="n">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="Q3" t="n">
         <v>4</v>
@@ -789,7 +833,7 @@
         <v>0.2</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.9</v>
+        <v>5.9</v>
       </c>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr">
@@ -807,13 +851,32 @@
         </is>
       </c>
       <c r="AF3" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>66.27</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AJ3" t="n">
+        <v>5823.98</v>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>PMKNS</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GM3CH90 04008-L10VTH</t>
+          <t>GM3CH90 03006-L12VTH</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -833,17 +896,17 @@
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="G4" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>HA-4</t>
+          <t>HA-3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -860,14 +923,14 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="P4" t="n">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="Q4" t="n">
         <v>3</v>
@@ -899,7 +962,7 @@
         <v>0.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr">
@@ -917,13 +980,32 @@
         </is>
       </c>
       <c r="AF4" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>62.97</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AJ4" t="n">
+        <v>5533.97</v>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>PMKNS</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GM3CH90 03006-L12VTH</t>
+          <t>GM4CH9006006-L25VTH</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -943,17 +1025,17 @@
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>2.9</v>
+        <v>5.9</v>
       </c>
       <c r="G5" t="n">
-        <v>2.9</v>
+        <v>5.9</v>
       </c>
       <c r="H5" t="n">
         <v>0.6</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>HA-3</t>
+          <t>HA-6</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -970,17 +1052,17 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="P5" t="n">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="Q5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
@@ -1009,7 +1091,7 @@
         <v>0.2</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.9</v>
+        <v>5.9</v>
       </c>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr">
@@ -1029,11 +1111,30 @@
       <c r="AF5" t="n">
         <v>0.6</v>
       </c>
+      <c r="AG5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>70.83</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AJ5" t="n">
+        <v>6224.72</v>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>PMKNS</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GM4CH9006006-L25VTH</t>
+          <t>GM4CH90 05011-L12VTH</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1053,17 +1154,17 @@
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>5.9</v>
+        <v>4.95</v>
       </c>
       <c r="G6" t="n">
-        <v>5.9</v>
+        <v>4.95</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>HA-6</t>
+          <t>HA-5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1080,14 +1181,14 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="P6" t="n">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="Q6" t="n">
         <v>4</v>
@@ -1119,7 +1220,7 @@
         <v>0.2</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.9</v>
+        <v>4.95</v>
       </c>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr">
@@ -1137,7 +1238,26 @@
         </is>
       </c>
       <c r="AF6" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>79.72</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
+        <v>7006</v>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>PMKNS</t>
+        </is>
       </c>
     </row>
   </sheetData>
